--- a/gte/nodes/LPC/compressor_stage_1_blade_stator_coordinates_lattice.xlsx
+++ b/gte/nodes/LPC/compressor_stage_1_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>10.8502736910071</v>
+        <v>10.840741899657756</v>
       </c>
       <c r="B1">
-        <v>11.759777122736431</v>
+        <v>11.768564577347602</v>
       </c>
       <c r="C1">
         <v>384.89451392788493</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9.8691136627779112</v>
+        <v>9.9026600972369749</v>
       </c>
       <c r="B2">
-        <v>11.544549944535763</v>
+        <v>11.503496103876131</v>
       </c>
       <c r="C2">
         <v>384.89451392788493</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>9.0024855324192252</v>
+        <v>9.052546659026719</v>
       </c>
       <c r="B3">
-        <v>11.198178059960394</v>
+        <v>11.137864062901837</v>
       </c>
       <c r="C3">
         <v>384.89451392788493</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>8.1585642849870812</v>
+        <v>8.2214505883588078</v>
       </c>
       <c r="B4">
-        <v>10.825805667670982</v>
+        <v>10.750491770852809</v>
       </c>
       <c r="C4">
         <v>384.89451392788493</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>7.3321842195700713</v>
+        <v>7.4054769034704506</v>
       </c>
       <c r="B5">
-        <v>10.433347751544003</v>
+        <v>10.345831888238768</v>
       </c>
       <c r="C5">
         <v>384.89451392788493</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>6.5212048488244019</v>
+        <v>6.6030027755306211</v>
       </c>
       <c r="B6">
-        <v>10.023255275803569</v>
+        <v>9.9257395985470787</v>
       </c>
       <c r="C6">
         <v>384.89451392788493</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>5.7243836812799991</v>
+        <v>5.8130809169854825</v>
       </c>
       <c r="B7">
-        <v>9.596950954837947</v>
+        <v>9.49129782081028</v>
       </c>
       <c r="C7">
         <v>384.89451392788493</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>4.9409699470367165</v>
+        <v>5.03513386564926</v>
       </c>
       <c r="B8">
-        <v>9.1552944574375861</v>
+        <v>9.0431666975468978</v>
       </c>
       <c r="C8">
         <v>384.89451392788493</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>4.1698255213265947</v>
+        <v>4.2682948704256223</v>
       </c>
       <c r="B9">
-        <v>8.6995889929379349</v>
+        <v>8.582337080220011</v>
       </c>
       <c r="C9">
         <v>384.89451392788493</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>3.4097281131756989</v>
+        <v>3.5116347094780291</v>
       </c>
       <c r="B10">
-        <v>8.2312341451567868</v>
+        <v>8.109871235517458</v>
       </c>
       <c r="C10">
         <v>384.89451392788493</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>2.659506121654</v>
+        <v>2.7642635669196149</v>
       </c>
       <c r="B11">
-        <v>7.7515714552963244</v>
+        <v>7.6267863820814963</v>
       </c>
       <c r="C11">
         <v>384.89451392788493</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.9185183366657415</v>
+        <v>2.0256904461747558</v>
       </c>
       <c r="B12">
-        <v>7.2613351407343814</v>
+        <v>7.1336438167796965</v>
       </c>
       <c r="C12">
         <v>384.89451392788493</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>1.1881944214083531</v>
+        <v>1.2969802219631295</v>
       </c>
       <c r="B13">
-        <v>6.7588881661670035</v>
+        <v>6.6292261974264246</v>
       </c>
       <c r="C13">
         <v>384.89451392788493</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>0.46937910795436966</v>
+        <v>0.57875931366446753</v>
       </c>
       <c r="B14">
-        <v>6.2432632714537766</v>
+        <v>6.1128174146777861</v>
       </c>
       <c r="C14">
         <v>384.89451392788493</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-0.24149346941649458</v>
+        <v>-0.13165555199661383</v>
       </c>
       <c r="B15">
-        <v>5.7185435497901542</v>
+        <v>5.5874849296100333</v>
       </c>
       <c r="C15">
         <v>384.89451392788493</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-0.94769380932687364</v>
+        <v>-0.83672536392006591</v>
       </c>
       <c r="B16">
-        <v>5.1884738843880553</v>
+        <v>5.05604209251773</v>
       </c>
       <c r="C16">
         <v>384.89451392788493</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-1.6469003442160259</v>
+        <v>-1.5347122808490257</v>
       </c>
       <c r="B17">
-        <v>4.6503959651893769</v>
+        <v>4.5165022401485517</v>
       </c>
       <c r="C17">
         <v>384.89451392788493</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-2.3361069453557914</v>
+        <v>-2.2233638575949666</v>
       </c>
       <c r="B18">
-        <v>4.100867625629963</v>
+        <v>3.9662904249540762</v>
       </c>
       <c r="C18">
         <v>384.89451392788493</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.015161305531735</v>
+        <v>-2.9025680633995545</v>
       </c>
       <c r="B19">
-        <v>3.5397144663914926</v>
+        <v>3.40527857574839</v>
       </c>
       <c r="C19">
         <v>384.89451392788493</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-3.6846245729078628</v>
+        <v>-3.5727479711120087</v>
       </c>
       <c r="B20">
-        <v>2.9675790299670872</v>
+        <v>2.8339503404361888</v>
       </c>
       <c r="C20">
         <v>384.89451392788493</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-4.3450578956481687</v>
+        <v>-4.2343266535815429</v>
       </c>
       <c r="B21">
-        <v>2.3851038588498756</v>
+        <v>2.2527893669221815</v>
       </c>
       <c r="C21">
         <v>384.89451392788493</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-4.9969214850606836</v>
+        <v>-4.8876508154618481</v>
       </c>
       <c r="B22">
-        <v>1.7928159178242031</v>
+        <v>1.6621920006102826</v>
       </c>
       <c r="C22">
         <v>384.89451392788493</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-5.64027180502955</v>
+        <v>-5.5327616886245012</v>
       </c>
       <c r="B23">
-        <v>1.190779860839267</v>
+        <v>1.0622053769012465</v>
       </c>
       <c r="C23">
         <v>384.89451392788493</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-6.27506438258294</v>
+        <v>-6.1696241367455542</v>
       </c>
       <c r="B24">
-        <v>0.57894476413548457</v>
+        <v>0.45278932869503979</v>
       </c>
       <c r="C24">
         <v>384.89451392788493</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-6.9012547447490258</v>
+        <v>-6.7982030235010642</v>
       </c>
       <c r="B25">
-        <v>-0.042740296046734315</v>
+        <v>-0.16609631110837442</v>
       </c>
       <c r="C25">
         <v>384.89451392788493</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-7.5187798998693491</v>
+        <v>-7.41844872790005</v>
       </c>
       <c r="B26">
-        <v>-0.67434744828208382</v>
+        <v>-0.79450826817303433</v>
       </c>
       <c r="C26">
         <v>384.89451392788493</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-8.1275027815389773</v>
+        <v>-8.030253690283466</v>
       </c>
       <c r="B27">
-        <v>-1.3160336404057595</v>
+        <v>-1.4325695024190506</v>
       </c>
       <c r="C27">
         <v>384.89451392788493</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-8.7272678046663437</v>
+        <v>-8.63349586632522</v>
       </c>
       <c r="B28">
-        <v>-1.9679770250680533</v>
+        <v>-2.0804195323305272</v>
       </c>
       <c r="C28">
         <v>384.89451392788493</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-9.3179193841598824</v>
+        <v>-9.2280532116992315</v>
       </c>
       <c r="B29">
-        <v>-2.6303557549192651</v>
+        <v>-2.7381978763915766</v>
       </c>
       <c r="C29">
         <v>384.89451392788493</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-9.899373004891018</v>
+        <v>-9.8138564172737652</v>
       </c>
       <c r="B30">
-        <v>-3.3032666039754313</v>
+        <v>-3.4059837673310329</v>
       </c>
       <c r="C30">
         <v>384.89451392788493</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-10.471828431583143</v>
+        <v>-10.391047114694494</v>
       </c>
       <c r="B31">
-        <v>-3.98648083171552</v>
+        <v>-4.0836152948566244</v>
       </c>
       <c r="C31">
         <v>384.89451392788493</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-11.035556498922645</v>
+        <v>-10.959819670801435</v>
       </c>
       <c r="B32">
-        <v>-4.67968831898424</v>
+        <v>-4.77087026292081</v>
       </c>
       <c r="C32">
         <v>384.89451392788493</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-11.590828041595906</v>
+        <v>-11.520368452434612</v>
       </c>
       <c r="B33">
-        <v>-5.382578946626297</v>
+        <v>-5.4675264754760446</v>
       </c>
       <c r="C33">
         <v>384.89451392788493</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-12.137792437435714</v>
+        <v>-12.072795948780755</v>
       </c>
       <c r="B34">
-        <v>-6.0949816696107062</v>
+        <v>-6.17346676905861</v>
       </c>
       <c r="C34">
         <v>384.89451392788493</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-12.676113236860468</v>
+        <v>-12.616837138413445</v>
       </c>
       <c r="B35">
-        <v>-6.8172817394037377</v>
+        <v>-6.888994110540116</v>
       </c>
       <c r="C35">
         <v>384.89451392788493</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-13.205332533434966</v>
+        <v>-13.152135122252973</v>
       </c>
       <c r="B36">
-        <v>-7.5500034815959642</v>
+        <v>-7.6145164993759957</v>
       </c>
       <c r="C36">
         <v>384.89451392788493</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-13.724992420724012</v>
+        <v>-13.67833300121964</v>
       </c>
       <c r="B37">
-        <v>-8.2936712217779647</v>
+        <v>-8.3504419350216867</v>
       </c>
       <c r="C37">
         <v>384.89451392788493</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-14.234341106808133</v>
+        <v>-14.194852559956878</v>
       </c>
       <c r="B38">
-        <v>-9.0491457990030515</v>
+        <v>-9.0974314210045826</v>
       </c>
       <c r="C38">
         <v>384.89451392788493</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-14.731451257830688</v>
+        <v>-14.700230318000674</v>
       </c>
       <c r="B39">
-        <v>-9.8186341061753932</v>
+        <v>-9.8571579771398348</v>
       </c>
       <c r="C39">
         <v>384.89451392788493</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-15.214101654450777</v>
+        <v>-15.19278147861016</v>
       </c>
       <c r="B40">
-        <v>-10.60467954966191</v>
+        <v>-10.631547627314557</v>
       </c>
       <c r="C40">
         <v>384.89451392788493</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-15.680071077327481</v>
+        <v>-15.670821245044454</v>
       </c>
       <c r="B41">
-        <v>-11.409825535829494</v>
+        <v>-11.422526395415853</v>
       </c>
       <c r="C41">
         <v>384.89451392788493</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-15.680071077327481</v>
+        <v>-15.670821245044454</v>
       </c>
       <c r="B42">
-        <v>-11.409825535829494</v>
+        <v>-11.422526395415853</v>
       </c>
       <c r="C42">
         <v>384.89451392788493</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-15.112413106658812</v>
+        <v>-15.116444335582163</v>
       </c>
       <c r="B43">
-        <v>-10.721117982882721</v>
+        <v>-10.718814629546136</v>
       </c>
       <c r="C43">
         <v>384.89451392788493</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-14.545538366098358</v>
+        <v>-14.560666332526582</v>
       </c>
       <c r="B44">
-        <v>-10.031513592596509</v>
+        <v>-10.01670456414465</v>
       </c>
       <c r="C44">
         <v>384.89451392788493</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-13.9773642054455</v>
+        <v>-14.001941136791091</v>
       </c>
       <c r="B45">
-        <v>-9.34339710279606</v>
+        <v>-9.317963666883</v>
       </c>
       <c r="C45">
         <v>384.89451392788493</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-13.405807974499608</v>
+        <v>-13.438722649289046</v>
       </c>
       <c r="B46">
-        <v>-8.6591532513065435</v>
+        <v>-8.62435940543275</v>
       </c>
       <c r="C46">
         <v>384.89451392788493</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-12.829075331766434</v>
+        <v>-12.869680505260664</v>
       </c>
       <c r="B47">
-        <v>-7.9808366481778883</v>
+        <v>-7.9374126245603982</v>
       </c>
       <c r="C47">
         <v>384.89451392788493</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-12.246525170577169</v>
+        <v>-12.294347277253493</v>
       </c>
       <c r="B48">
-        <v>-7.3091813923589228</v>
+        <v>-7.257657677411955</v>
       </c>
       <c r="C48">
         <v>384.89451392788493</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-11.657804692969368</v>
+        <v>-11.712471272141926</v>
       </c>
       <c r="B49">
-        <v>-6.6445914550232121</v>
+        <v>-6.5853822942283351</v>
       </c>
       <c r="C49">
         <v>384.89451392788493</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-11.062561100980602</v>
+        <v>-11.123800796800358</v>
       </c>
       <c r="B50">
-        <v>-5.9874708073443248</v>
+        <v>-5.9208742052504526</v>
       </c>
       <c r="C50">
         <v>384.89451392788493</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-10.460557454450525</v>
+        <v>-10.528170431512205</v>
       </c>
       <c r="B51">
-        <v>-5.3380907575633261</v>
+        <v>-5.2643225147885246</v>
       </c>
       <c r="C51">
         <v>384.89451392788493</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-9.8520202444271625</v>
+        <v>-9.9257598501969788</v>
       </c>
       <c r="B52">
-        <v>-4.6961919621912642</v>
+        <v>-4.6155218234299848</v>
       </c>
       <c r="C52">
         <v>384.89451392788493</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-9.2372918197606282</v>
+        <v>-9.3168350001832163</v>
       </c>
       <c r="B53">
-        <v>-4.0613824148066877</v>
+        <v>-3.9741681058315739</v>
       </c>
       <c r="C53">
         <v>384.89451392788493</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-8.6167145293010421</v>
+        <v>-8.7016618287994447</v>
       </c>
       <c r="B54">
-        <v>-3.4332701089881428</v>
+        <v>-3.3399573366500266</v>
       </c>
       <c r="C54">
         <v>384.89451392788493</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-7.9905547228069533</v>
+        <v>-8.08044861447983</v>
       </c>
       <c r="B55">
-        <v>-2.8115500610452564</v>
+        <v>-2.7126514163985478</v>
       </c>
       <c r="C55">
         <v>384.89451392788493</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-7.3587747536706436</v>
+        <v>-7.453172960081023</v>
       </c>
       <c r="B56">
-        <v>-2.1962653782119688</v>
+        <v>-2.0922759490161971</v>
       </c>
       <c r="C56">
         <v>384.89451392788493</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-6.721260976192827</v>
+        <v>-6.8197547995653069</v>
       </c>
       <c r="B57">
-        <v>-1.5875461904532981</v>
+        <v>-1.4789224642984964</v>
       </c>
       <c r="C57">
         <v>384.89451392788493</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-6.0778997446742276</v>
+        <v>-6.1801140668949728</v>
       </c>
       <c r="B58">
-        <v>-0.98552262773427124</v>
+        <v>-0.87268249204097792</v>
       </c>
       <c r="C58">
         <v>384.89451392788493</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-5.4285912742549112</v>
+        <v>-5.5341805185322013</v>
       </c>
       <c r="B59">
-        <v>-0.3903089486710174</v>
+        <v>-0.27363633316565894</v>
       </c>
       <c r="C59">
         <v>384.89451392788493</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-4.7732912234324365</v>
+        <v>-4.8819232009388491</v>
       </c>
       <c r="B60">
-        <v>0.19804407351583023</v>
+        <v>0.31818062689938909</v>
       </c>
       <c r="C60">
         <v>384.89451392788493</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.1119691115437149</v>
+        <v>-4.2233209830766727</v>
       </c>
       <c r="B61">
-        <v>0.77950153695452529</v>
+        <v>0.90274423159959916</v>
       </c>
       <c r="C61">
         <v>384.89451392788493</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.4445944579256627</v>
+        <v>-3.558352733907435</v>
       </c>
       <c r="B62">
-        <v>1.3540285397733209</v>
+        <v>1.4800303243804016</v>
       </c>
       <c r="C62">
         <v>384.89451392788493</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-2.7712329604304262</v>
+        <v>-2.8870689278346298</v>
       </c>
       <c r="B63">
-        <v>1.9217003092729919</v>
+        <v>2.0500966065089368</v>
       </c>
       <c r="C63">
         <v>384.89451392788493</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.0923350309710891</v>
+        <v>-2.2098064610286956</v>
       </c>
       <c r="B64">
-        <v>2.4830325894444032</v>
+        <v>2.6133282105391764</v>
       </c>
       <c r="C64">
         <v>384.89451392788493</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.4084472599759728</v>
+        <v>-1.5269738351018041</v>
       </c>
       <c r="B65">
-        <v>3.0386512534509387</v>
+        <v>3.1701921268467972</v>
       </c>
       <c r="C65">
         <v>384.89451392788493</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.72011623787338852</v>
+        <v>-0.8389795516661217</v>
       </c>
       <c r="B66">
-        <v>3.5891821744559933</v>
+        <v>3.7211553458074849</v>
       </c>
       <c r="C66">
         <v>384.89451392788493</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.027171229788651528</v>
+        <v>-0.14569313521259603</v>
       </c>
       <c r="B67">
-        <v>4.13442985255582</v>
+        <v>4.2660687105876374</v>
       </c>
       <c r="C67">
         <v>384.89451392788493</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.67342780036495609</v>
+        <v>0.55517179825274876</v>
       </c>
       <c r="B68">
-        <v>4.670913295578158</v>
+        <v>4.8023184755165325</v>
       </c>
       <c r="C68">
         <v>384.89451392788493</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1.3840419773972512</v>
+        <v>1.2653926839226495</v>
       </c>
       <c r="B69">
-        <v>5.19592889845181</v>
+        <v>5.3278727143944469</v>
       </c>
       <c r="C69">
         <v>384.89451392788493</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2.1014474797983875</v>
+        <v>1.9825552532999626</v>
       </c>
       <c r="B70">
-        <v>5.713168096778328</v>
+        <v>5.8454913677427367</v>
       </c>
       <c r="C70">
         <v>384.89451392788493</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.8221295436710574</v>
+        <v>2.7040273823259278</v>
       </c>
       <c r="B71">
-        <v>6.2266554696300949</v>
+        <v>6.3581834239384758</v>
       </c>
       <c r="C71">
         <v>384.89451392788493</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.5469945818877093</v>
+        <v>3.430497228385164</v>
       </c>
       <c r="B72">
-        <v>6.7353531292900373</v>
+        <v>6.8651621960604921</v>
       </c>
       <c r="C72">
         <v>384.89451392788493</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.2775391325739731</v>
+        <v>4.163096603147733</v>
       </c>
       <c r="B73">
-        <v>7.2375474653429555</v>
+        <v>7.365133821021705</v>
       </c>
       <c r="C73">
         <v>384.89451392788493</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.0131990580983947</v>
+        <v>4.9014116539820645</v>
       </c>
       <c r="B74">
-        <v>7.7338844433705551</v>
+        <v>7.85857140636964</v>
       </c>
       <c r="C74">
         <v>384.89451392788493</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5.7528850831875333</v>
+        <v>5.6446349670096225</v>
       </c>
       <c r="B75">
-        <v>8.2256113376130475</v>
+        <v>8.3463979705189875</v>
       </c>
       <c r="C75">
         <v>384.89451392788493</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6.4954680577570727</v>
+        <v>6.3919305476656589</v>
       </c>
       <c r="B76">
-        <v>8.7140210809477718</v>
+        <v>8.8295692047185135</v>
       </c>
       <c r="C76">
         <v>384.89451392788493</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7.2399086923140326</v>
+        <v>7.1425305717921805</v>
       </c>
       <c r="B77">
-        <v>9.2003037114159216</v>
+        <v>9.3089628692543851</v>
       </c>
       <c r="C77">
         <v>384.89451392788493</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>7.9855670145416306</v>
+        <v>7.8959684775443977</v>
       </c>
       <c r="B78">
-        <v>9.6851920290769691</v>
+        <v>9.7851123277283172</v>
       </c>
       <c r="C78">
         <v>384.89451392788493</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8.73131686270683</v>
+        <v>8.6514134149938418</v>
       </c>
       <c r="B79">
-        <v>10.169975544997751</v>
+        <v>10.258967390150032</v>
       </c>
       <c r="C79">
         <v>384.89451392788493</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>9.47514542665397</v>
+        <v>9.4073703509099982</v>
       </c>
       <c r="B80">
-        <v>10.656959026686369</v>
+        <v>10.732237146787895</v>
       </c>
       <c r="C80">
         <v>384.89451392788493</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>10.212023782124687</v>
+        <v>10.160081207034649</v>
       </c>
       <c r="B81">
-        <v>11.151900841964411</v>
+        <v>11.209217752969936</v>
       </c>
       <c r="C81">
         <v>384.89451392788493</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>10.8502736910071</v>
+        <v>10.840741899657756</v>
       </c>
       <c r="B82">
-        <v>11.759777122736431</v>
+        <v>11.768564577347602</v>
       </c>
       <c r="C82">
         <v>384.89451392788493</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>11.003593683677961</v>
+        <v>11.031951259886732</v>
       </c>
       <c r="B1">
-        <v>13.888760125949698</v>
+        <v>13.866246182407533</v>
       </c>
       <c r="C1">
         <v>452.5754307907855</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9.8294268397483844</v>
+        <v>9.90848986611056</v>
       </c>
       <c r="B2">
-        <v>13.68003798103195</v>
+        <v>13.609036180433908</v>
       </c>
       <c r="C2">
         <v>452.5754307907855</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>8.8561823194822189</v>
+        <v>8.9537602110961334</v>
       </c>
       <c r="B3">
-        <v>13.272159698435871</v>
+        <v>13.183892725009747</v>
       </c>
       <c r="C3">
         <v>452.5754307907855</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>7.9192629520356306</v>
+        <v>8.03086004678058</v>
       </c>
       <c r="B4">
-        <v>12.828275575352697</v>
+        <v>12.727070367122657</v>
       </c>
       <c r="C4">
         <v>452.5754307907855</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>7.0094399972571981</v>
+        <v>7.1320994110655667</v>
       </c>
       <c r="B5">
-        <v>12.357533227690313</v>
+        <v>12.246222686955919</v>
       </c>
       <c r="C5">
         <v>452.5754307907855</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>6.1229064827151243</v>
+        <v>6.25429832643947</v>
       </c>
       <c r="B6">
-        <v>11.863706163100538</v>
+        <v>11.744514617256272</v>
       </c>
       <c r="C6">
         <v>452.5754307907855</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>5.2574627932610918</v>
+        <v>5.395614814860588</v>
       </c>
       <c r="B7">
-        <v>11.348974661252305</v>
+        <v>11.223779421498586</v>
       </c>
       <c r="C7">
         <v>452.5754307907855</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>4.4117896168166162</v>
+        <v>4.5549396053941242</v>
       </c>
       <c r="B8">
-        <v>10.814646436953762</v>
+        <v>10.685121122555261</v>
       </c>
       <c r="C8">
         <v>452.5754307907855</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>3.58387033325277</v>
+        <v>3.7305848293650463</v>
       </c>
       <c r="B9">
-        <v>10.262720383452407</v>
+        <v>10.130219603640027</v>
       </c>
       <c r="C9">
         <v>452.5754307907855</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2.7715360711190278</v>
+        <v>2.920736623683803</v>
       </c>
       <c r="B10">
-        <v>9.6953463069685366</v>
+        <v>9.5608801462900175</v>
       </c>
       <c r="C10">
         <v>452.5754307907855</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.9727062617289426</v>
+        <v>2.1236557453430254</v>
       </c>
       <c r="B11">
-        <v>9.1145864871742663</v>
+        <v>8.9788337649946222</v>
       </c>
       <c r="C11">
         <v>452.5754307907855</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>1.1862500124826123</v>
+        <v>1.3383933176706973</v>
       </c>
       <c r="B12">
-        <v>8.5215618756802538</v>
+        <v>8.38502484720341</v>
       </c>
       <c r="C12">
         <v>452.5754307907855</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>0.41474683236222615</v>
+        <v>0.56708730925401685</v>
       </c>
       <c r="B13">
-        <v>7.9137156383994043</v>
+        <v>7.7773255392543978</v>
       </c>
       <c r="C13">
         <v>452.5754307907855</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-0.34027374012526607</v>
+        <v>-0.18899694652240676</v>
       </c>
       <c r="B14">
-        <v>7.2895316820678211</v>
+        <v>7.1544764941711225</v>
       </c>
       <c r="C14">
         <v>452.5754307907855</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.0851924499559948</v>
+        <v>-0.93517150234357238</v>
       </c>
       <c r="B15">
-        <v>6.65533466241208</v>
+        <v>6.521764632830763</v>
       </c>
       <c r="C15">
         <v>452.5754307907855</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-1.8258615530624753</v>
+        <v>-1.67630841487684</v>
       </c>
       <c r="B16">
-        <v>6.0169253917410144</v>
+        <v>5.88403896175433</v>
       </c>
       <c r="C16">
         <v>452.5754307907855</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-2.5581090657197052</v>
+        <v>-2.4089423706494504</v>
       </c>
       <c r="B17">
-        <v>5.3701685597019422</v>
+        <v>5.2378505621845042</v>
       </c>
       <c r="C17">
         <v>452.5754307907855</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-3.2765370374627221</v>
+        <v>-3.1285878752797389</v>
       </c>
       <c r="B18">
-        <v>4.7097136659304546</v>
+        <v>4.5787351610244</v>
       </c>
       <c r="C18">
         <v>452.5754307907855</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-3.9808678905242609</v>
+        <v>-3.8350160808905729</v>
       </c>
       <c r="B19">
-        <v>4.0352855726766723</v>
+        <v>3.9064649930971593</v>
       </c>
       <c r="C19">
         <v>452.5754307907855</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-4.6721041403114851</v>
+        <v>-4.52906230123096</v>
       </c>
       <c r="B20">
-        <v>3.3478779828443406</v>
+        <v>3.2218714202059191</v>
       </c>
       <c r="C20">
         <v>452.5754307907855</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-5.3512483022315536</v>
+        <v>-5.211561850049903</v>
       </c>
       <c r="B21">
-        <v>2.6484845993372139</v>
+        <v>2.5257858041538297</v>
       </c>
       <c r="C21">
         <v>452.5754307907855</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-6.0191230873989294</v>
+        <v>-5.8831999921901872</v>
       </c>
       <c r="B22">
-        <v>1.9379209013165661</v>
+        <v>1.8188901677329388</v>
       </c>
       <c r="C22">
         <v>452.5754307907855</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-6.6758319897572989</v>
+        <v>-6.5440617968697454</v>
       </c>
       <c r="B23">
-        <v>1.2162894729737463</v>
+        <v>1.1012691776909165</v>
       </c>
       <c r="C23">
         <v>452.5754307907855</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-7.3212986989576549</v>
+        <v>-7.1940822844002961</v>
       </c>
       <c r="B24">
-        <v>0.48351467475762477</v>
+        <v>0.37285816176433129</v>
       </c>
       <c r="C24">
         <v>452.5754307907855</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-7.9554469046509855</v>
+        <v>-7.8331964750935468</v>
       </c>
       <c r="B25">
-        <v>-0.26047913288292091</v>
+        <v>-0.36640755231023925</v>
       </c>
       <c r="C25">
         <v>452.5754307907855</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-8.5781682310983118</v>
+        <v>-8.4613122168242647</v>
       </c>
       <c r="B26">
-        <v>-1.0157993730216421</v>
+        <v>-1.1166196806778828</v>
       </c>
       <c r="C26">
         <v>452.5754307907855</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-9.18922604100078</v>
+        <v>-9.0782286677194115</v>
       </c>
       <c r="B27">
-        <v>-1.78268060282278</v>
+        <v>-1.8779781150103529</v>
       </c>
       <c r="C27">
         <v>452.5754307907855</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-9.78835163166957</v>
+        <v>-9.6837178134689879</v>
       </c>
       <c r="B28">
-        <v>-2.5613891629731911</v>
+        <v>-2.6507097908610548</v>
       </c>
       <c r="C28">
         <v>452.5754307907855</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-10.375276300415859</v>
+        <v>-10.277551639763</v>
       </c>
       <c r="B29">
-        <v>-3.3521913941597341</v>
+        <v>-3.4350416437833986</v>
       </c>
       <c r="C29">
         <v>452.5754307907855</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-10.949859957999353</v>
+        <v>-10.85960855628548</v>
       </c>
       <c r="B30">
-        <v>-4.1552261541833673</v>
+        <v>-4.231094688838434</v>
       </c>
       <c r="C30">
         <v>452.5754307907855</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-11.512476968973877</v>
+        <v>-11.430192668696554</v>
       </c>
       <c r="B31">
-        <v>-4.9701223693014267</v>
+        <v>-5.038566259117748</v>
       </c>
       <c r="C31">
         <v>452.5754307907855</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-12.063630311341804</v>
+        <v>-11.989714506650394</v>
       </c>
       <c r="B32">
-        <v>-5.796381482885371</v>
+        <v>-5.8570477672205961</v>
       </c>
       <c r="C32">
         <v>452.5754307907855</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-12.603822963105484</v>
+        <v>-12.538584599801151</v>
       </c>
       <c r="B33">
-        <v>-6.6335049383066345</v>
+        <v>-6.6861306257462036</v>
       </c>
       <c r="C33">
         <v>452.5754307907855</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-13.133341476821816</v>
+        <v>-13.077032875896654</v>
       </c>
       <c r="B34">
-        <v>-7.4812087019176321</v>
+        <v>-7.5255859947559838</v>
       </c>
       <c r="C34">
         <v>452.5754307907855</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-13.651606703265813</v>
+        <v>-13.604566855059398</v>
       </c>
       <c r="B35">
-        <v>-8.3400668319946334</v>
+        <v>-8.3759040241600289</v>
       </c>
       <c r="C35">
         <v>452.5754307907855</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-14.157823067767025</v>
+        <v>-14.120513455505547</v>
       </c>
       <c r="B36">
-        <v>-9.210867909794862</v>
+        <v>-9.23775461133059</v>
       </c>
       <c r="C36">
         <v>452.5754307907855</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-14.651194995655011</v>
+        <v>-14.624199595451277</v>
       </c>
       <c r="B37">
-        <v>-10.094400516575572</v>
+        <v>-10.111807653639954</v>
       </c>
       <c r="C37">
         <v>452.5754307907855</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-15.130401311454873</v>
+        <v>-15.114514465868558</v>
       </c>
       <c r="B38">
-        <v>-10.991974214161337</v>
+        <v>-10.999168704776865</v>
       </c>
       <c r="C38">
         <v>452.5754307907855</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-15.592018436473941</v>
+        <v>-15.588596348752652</v>
       </c>
       <c r="B39">
-        <v>-11.906982486646097</v>
+        <v>-11.902685943696076</v>
       </c>
       <c r="C39">
         <v>452.5754307907855</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-16.0320971912151</v>
+        <v>-16.043145798854635</v>
       </c>
       <c r="B40">
-        <v>-12.843339798691151</v>
+        <v>-12.825643205668825</v>
       </c>
       <c r="C40">
         <v>452.5754307907855</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-16.446688396181223</v>
+        <v>-16.474863370925561</v>
       </c>
       <c r="B41">
-        <v>-13.804960614957766</v>
+        <v>-13.771324325966342</v>
       </c>
       <c r="C41">
         <v>452.5754307907855</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-16.446688396181223</v>
+        <v>-16.474863370925561</v>
       </c>
       <c r="B42">
-        <v>-13.804960614957766</v>
+        <v>-13.771324325966342</v>
       </c>
       <c r="C42">
         <v>452.5754307907855</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-15.849780669438797</v>
+        <v>-15.891523409656282</v>
       </c>
       <c r="B43">
-        <v>-13.024053686774298</v>
+        <v>-12.976548255455901</v>
       </c>
       <c r="C43">
         <v>452.5754307907855</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-15.25869681363638</v>
+        <v>-15.311391516553663</v>
       </c>
       <c r="B44">
-        <v>-12.237374081759283</v>
+        <v>-12.178579294443122</v>
       </c>
       <c r="C44">
         <v>452.5754307907855</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-14.669669637627308</v>
+        <v>-14.731349865729879</v>
       </c>
       <c r="B45">
-        <v>-11.448655875972516</v>
+        <v>-11.380520518096008</v>
       </c>
       <c r="C45">
         <v>452.5754307907855</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-14.078931950264899</v>
+        <v>-14.148280631297078</v>
       </c>
       <c r="B46">
-        <v>-10.661633145473783</v>
+        <v>-10.585475001582541</v>
       </c>
       <c r="C46">
         <v>452.5754307907855</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-13.483234770549638</v>
+        <v>-13.559496338939193</v>
       </c>
       <c r="B47">
-        <v>-9.8795263114460354</v>
+        <v>-9.7961175045316384</v>
       </c>
       <c r="C47">
         <v>452.5754307907855</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-12.881401958070637</v>
+        <v>-12.964030920627261</v>
       </c>
       <c r="B48">
-        <v>-9.103501175564924</v>
+        <v>-9.01340952441594</v>
       </c>
       <c r="C48">
         <v>452.5754307907855</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-12.272775582564151</v>
+        <v>-12.36134865990409</v>
       </c>
       <c r="B49">
-        <v>-8.3342098846292441</v>
+        <v>-8.23788424316899</v>
       </c>
       <c r="C49">
         <v>452.5754307907855</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-11.65669771376645</v>
+        <v>-11.750913840312496</v>
       </c>
       <c r="B50">
-        <v>-7.57230458543782</v>
+        <v>-7.4700748427243537</v>
       </c>
       <c r="C50">
         <v>452.5754307907855</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-11.032719475371186</v>
+        <v>-11.132363990759556</v>
       </c>
       <c r="B51">
-        <v>-6.8182302084983091</v>
+        <v>-6.7103420792910153</v>
       </c>
       <c r="C51">
         <v>452.5754307907855</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-10.401228206901564</v>
+        <v>-10.506029621609416</v>
       </c>
       <c r="B52">
-        <v>-6.0716028191537488</v>
+        <v>-5.9583570061796252</v>
       </c>
       <c r="C52">
         <v>452.5754307907855</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-9.7628203018381825</v>
+        <v>-9.8724144885905041</v>
       </c>
       <c r="B53">
-        <v>-5.33183126645603</v>
+        <v>-5.2136182509762756</v>
       </c>
       <c r="C53">
         <v>452.5754307907855</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-9.1180921536616228</v>
+        <v>-9.2320223474312169</v>
       </c>
       <c r="B54">
-        <v>-4.59832439945702</v>
+        <v>-4.4756244412670272</v>
       </c>
       <c r="C54">
         <v>452.5754307907855</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-8.4675050904593938</v>
+        <v>-8.585244091002993</v>
       </c>
       <c r="B55">
-        <v>-3.8706249453239594</v>
+        <v>-3.7439865335304408</v>
       </c>
       <c r="C55">
         <v>452.5754307907855</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-7.8109801787466271</v>
+        <v>-7.9320191607493147</v>
       </c>
       <c r="B56">
-        <v>-3.1488111436854349</v>
+        <v>-3.018764799814952</v>
       </c>
       <c r="C56">
         <v>452.5754307907855</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-7.1483034196453659</v>
+        <v>-7.2721741352566784</v>
       </c>
       <c r="B57">
-        <v>-2.4330951122853808</v>
+        <v>-2.3001318410614737</v>
       </c>
       <c r="C57">
         <v>452.5754307907855</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-6.4792608142776542</v>
+        <v>-6.60553559311158</v>
       </c>
       <c r="B58">
-        <v>-1.7236889688677339</v>
+        <v>-1.5882602582109202</v>
       </c>
       <c r="C58">
         <v>452.5754307907855</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-5.803664351348913</v>
+        <v>-5.9319512198538975</v>
       </c>
       <c r="B59">
-        <v>-1.0207790720340877</v>
+        <v>-0.88330164510974385</v>
       </c>
       <c r="C59">
         <v>452.5754307907855</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-5.1214299698980978</v>
+        <v>-5.2513531288370512</v>
       </c>
       <c r="B60">
-        <v>-0.32444874381668509</v>
+        <v>-0.18532356722658019</v>
       </c>
       <c r="C60">
         <v>452.5754307907855</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.4324995965475518</v>
+        <v>-4.5636945403678508</v>
       </c>
       <c r="B61">
-        <v>0.3652444528945602</v>
+        <v>0.50562741706438374</v>
       </c>
       <c r="C61">
         <v>452.5754307907855</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.7368151579196125</v>
+        <v>-3.8689286747531</v>
       </c>
       <c r="B62">
-        <v>1.0482429552097436</v>
+        <v>1.1895047493889688</v>
       </c>
       <c r="C62">
         <v>452.5754307907855</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.0344921827957507</v>
+        <v>-3.1671526116473525</v>
       </c>
       <c r="B63">
-        <v>1.7246612763670624</v>
+        <v>1.8664050501089926</v>
       </c>
       <c r="C63">
         <v>452.5754307907855</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.3263406085939757</v>
+        <v>-2.459038868096171</v>
       </c>
       <c r="B64">
-        <v>2.3953022341171306</v>
+        <v>2.5369976545302753</v>
       </c>
       <c r="C64">
         <v>452.5754307907855</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.6133439748914329</v>
+        <v>-1.74540382049287</v>
       </c>
       <c r="B65">
-        <v>3.0611407223386657</v>
+        <v>3.2020950766946328</v>
       </c>
       <c r="C65">
         <v>452.5754307907855</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.89648582126525722</v>
+        <v>-1.0270638452307566</v>
       </c>
       <c r="B66">
-        <v>3.7231516349103915</v>
+        <v>3.8625098306438908</v>
       </c>
       <c r="C66">
         <v>452.5754307907855</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.17546454610259171</v>
+        <v>-0.30376611929650715</v>
       </c>
       <c r="B67">
-        <v>4.3810360214158459</v>
+        <v>4.5179902894935511</v>
       </c>
       <c r="C67">
         <v>452.5754307907855</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.5551620169694359</v>
+        <v>0.42901897794976218</v>
       </c>
       <c r="B68">
-        <v>5.0293995542578607</v>
+        <v>5.1640282626538685</v>
       </c>
       <c r="C68">
         <v>452.5754307907855</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1.299617443058025</v>
+        <v>1.1748082467592205</v>
       </c>
       <c r="B69">
-        <v>5.6640557852100439</v>
+        <v>5.7971235881777927</v>
       </c>
       <c r="C69">
         <v>452.5754307907855</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2.0521103774476388</v>
+        <v>1.9287904082015976</v>
       </c>
       <c r="B70">
-        <v>6.29074516070981</v>
+        <v>6.4220647823942762</v>
       </c>
       <c r="C70">
         <v>452.5754307907855</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.8063267652387438</v>
+        <v>2.6857199644514402</v>
       </c>
       <c r="B71">
-        <v>6.9157262326390718</v>
+        <v>7.0440725261981028</v>
       </c>
       <c r="C71">
         <v>452.5754307907855</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.5638766806185211</v>
+        <v>3.4469426212839669</v>
       </c>
       <c r="B72">
-        <v>7.5374030799938794</v>
+        <v>7.661807480471329</v>
       </c>
       <c r="C72">
         <v>452.5754307907855</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.3274269757616839</v>
+        <v>4.2146835133867491</v>
       </c>
       <c r="B73">
-        <v>8.1531322932755277</v>
+        <v>8.2730550378424077</v>
       </c>
       <c r="C73">
         <v>452.5754307907855</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.0959474857063176</v>
+        <v>4.9880942874960574</v>
       </c>
       <c r="B74">
-        <v>8.7639349818920955</v>
+        <v>8.8786595379380682</v>
       </c>
       <c r="C74">
         <v>452.5754307907855</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>5.867465273660291</v>
+        <v>5.7655431142704536</v>
       </c>
       <c r="B75">
-        <v>9.37176673974794</v>
+        <v>9.4802450897656687</v>
       </c>
       <c r="C75">
         <v>452.5754307907855</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6.6399333326471917</v>
+        <v>6.545337748008941</v>
       </c>
       <c r="B76">
-        <v>9.9786565798257332</v>
+        <v>10.079495932856792</v>
       </c>
       <c r="C76">
         <v>452.5754307907855</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7.4114644155155078</v>
+        <v>7.3259194307045208</v>
       </c>
       <c r="B77">
-        <v>10.586475159634743</v>
+        <v>10.677963450591532</v>
       </c>
       <c r="C77">
         <v>452.5754307907855</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8.1808843845975847</v>
+        <v>8.1063237714857461</v>
       </c>
       <c r="B78">
-        <v>11.196386295712269</v>
+        <v>11.276607471219787</v>
       </c>
       <c r="C78">
         <v>452.5754307907855</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>8.9461461171084817</v>
+        <v>8.8848609754893335</v>
       </c>
       <c r="B79">
-        <v>11.810419115831516</v>
+        <v>11.877109795030556</v>
       </c>
       <c r="C79">
         <v>452.5754307907855</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>9.7036101741539866</v>
+        <v>9.658518259059667</v>
       </c>
       <c r="B80">
-        <v>12.432181066792182</v>
+        <v>12.482468951924032</v>
       </c>
       <c r="C80">
         <v>452.5754307907855</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>10.444227440196531</v>
+        <v>10.419784920515477</v>
       </c>
       <c r="B81">
-        <v>13.070641718859076</v>
+        <v>13.100160109763881</v>
       </c>
       <c r="C81">
         <v>452.5754307907855</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>11.003593683677961</v>
+        <v>11.031951259886732</v>
       </c>
       <c r="B82">
-        <v>13.888760125949698</v>
+        <v>13.866246182407533</v>
       </c>
       <c r="C82">
         <v>452.5754307907855</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>11.081074970344902</v>
+        <v>11.148203512058567</v>
       </c>
       <c r="B1">
-        <v>15.691558128490108</v>
+        <v>15.643937402454444</v>
       </c>
       <c r="C1">
         <v>511.37584442281513</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>9.703633453472893</v>
+        <v>9.8281756230369588</v>
       </c>
       <c r="B2">
-        <v>15.502354022921528</v>
+        <v>15.408425345722458</v>
       </c>
       <c r="C2">
         <v>511.37584442281513</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>8.6281205295778154</v>
+        <v>8.7727376460078972</v>
       </c>
       <c r="B3">
-        <v>15.044668745893947</v>
+        <v>14.935596655835402</v>
       </c>
       <c r="C3">
         <v>511.37584442281513</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>7.6042589157865477</v>
+        <v>7.7637192019808339</v>
       </c>
       <c r="B4">
-        <v>14.541054051889546</v>
+        <v>14.421133244496929</v>
       </c>
       <c r="C4">
         <v>511.37584442281513</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>6.618045248340608</v>
+        <v>6.7889010224321282</v>
       </c>
       <c r="B5">
-        <v>14.003962022604775</v>
+        <v>13.875994848016752</v>
       </c>
       <c r="C5">
         <v>511.37584442281513</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>5.66371922882713</v>
+        <v>5.8432498618701914</v>
       </c>
       <c r="B6">
-        <v>13.438514834944414</v>
+        <v>13.30469589729252</v>
       </c>
       <c r="C6">
         <v>511.37584442281513</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>4.7379623546441785</v>
+        <v>4.923861988238583</v>
       </c>
       <c r="B7">
-        <v>12.847663370298243</v>
+        <v>12.709840814805917</v>
       </c>
       <c r="C7">
         <v>511.37584442281513</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>3.8387935796973083</v>
+        <v>4.0290000102966506</v>
       </c>
       <c r="B8">
-        <v>12.233169215970417</v>
+        <v>12.092987905771979</v>
       </c>
       <c r="C8">
         <v>511.37584442281513</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2.9631686981684489</v>
+        <v>3.156000980944043</v>
       </c>
       <c r="B9">
-        <v>11.597739342957425</v>
+        <v>11.456525627238696</v>
       </c>
       <c r="C9">
         <v>511.37584442281513</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2.1078106686968754</v>
+        <v>2.3019995491299081</v>
       </c>
       <c r="B10">
-        <v>10.944287764452826</v>
+        <v>10.803023976902031</v>
       </c>
       <c r="C10">
         <v>511.37584442281513</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>1.269574267474852</v>
+        <v>1.4642463038610853</v>
       </c>
       <c r="B11">
-        <v>10.275611278746158</v>
+        <v>10.134948963216887</v>
       </c>
       <c r="C11">
         <v>511.37584442281513</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>0.44675728936451836</v>
+        <v>0.64125015781210837</v>
       </c>
       <c r="B12">
-        <v>9.59322352197559</v>
+        <v>9.45363797588628</v>
       </c>
       <c r="C12">
         <v>511.37584442281513</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>-0.35670221364543248</v>
+        <v>-0.163562621729417</v>
       </c>
       <c r="B13">
-        <v>8.8936226965777774</v>
+        <v>8.756017918846716</v>
       </c>
       <c r="C13">
         <v>511.37584442281513</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>-1.1384641156734374</v>
+        <v>-0.948158116204773</v>
       </c>
       <c r="B14">
-        <v>8.17472791404909</v>
+        <v>8.0402645248733755</v>
       </c>
       <c r="C14">
         <v>511.37584442281513</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>-1.9082202523929805</v>
+        <v>-1.7209891565838844</v>
       </c>
       <c r="B15">
-        <v>7.445157355826229</v>
+        <v>7.3139593278626309</v>
       </c>
       <c r="C15">
         <v>511.37584442281513</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>-2.67485977114429</v>
+        <v>-2.4898084815351442</v>
       </c>
       <c r="B16">
-        <v>6.7128154362200361</v>
+        <v>6.5840559332057893</v>
       </c>
       <c r="C16">
         <v>511.37584442281513</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>-3.4320291043795739</v>
+        <v>-3.2490817109922285</v>
       </c>
       <c r="B17">
-        <v>5.972052431097536</v>
+        <v>5.845590431152659</v>
       </c>
       <c r="C17">
         <v>511.37584442281513</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>-4.171511588366168</v>
+        <v>-3.991649943849894</v>
       </c>
       <c r="B18">
-        <v>5.2155619125292647</v>
+        <v>5.0921418425563312</v>
       </c>
       <c r="C18">
         <v>511.37584442281513</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>-4.8928808895199483</v>
+        <v>-4.7171433135819552</v>
       </c>
       <c r="B19">
-        <v>4.4429647758435946</v>
+        <v>4.3233784258245107</v>
       </c>
       <c r="C19">
         <v>511.37584442281513</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>-5.5976582567939444</v>
+        <v>-5.4268892123070005</v>
       </c>
       <c r="B20">
-        <v>3.655613747183347</v>
+        <v>3.5404907487535446</v>
       </c>
       <c r="C20">
         <v>511.37584442281513</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>-6.2873649391411615</v>
+        <v>-6.1222150321436049</v>
       </c>
       <c r="B21">
-        <v>2.8548615526913581</v>
+        <v>2.7446693791397978</v>
       </c>
       <c r="C21">
         <v>511.37584442281513</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>-6.9632498350655556</v>
+        <v>-6.8042103167249186</v>
       </c>
       <c r="B22">
-        <v>2.0418187388384514</v>
+        <v>1.9368915531323898</v>
       </c>
       <c r="C22">
         <v>511.37584442281513</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>-7.6254724412747654</v>
+        <v>-7.4730132157423359</v>
       </c>
       <c r="B23">
-        <v>1.2166271334074457</v>
+        <v>1.1172811802915412</v>
       </c>
       <c r="C23">
         <v>511.37584442281513</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>-8.27391990402736</v>
+        <v>-8.1285240304018132</v>
       </c>
       <c r="B24">
-        <v>0.37918638450916592</v>
+        <v>0.28574883853024369</v>
       </c>
       <c r="C24">
         <v>511.37584442281513</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-8.9084793695819151</v>
+        <v>-8.7706430619093076</v>
       </c>
       <c r="B25">
-        <v>-0.47060385974557073</v>
+        <v>-0.55779489423851081</v>
       </c>
       <c r="C25">
         <v>511.37584442281513</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-9.5289902843738865</v>
+        <v>-9.3992285904881054</v>
       </c>
       <c r="B26">
-        <v>-1.3328863669186666</v>
+        <v>-1.4134771296646225</v>
       </c>
       <c r="C26">
         <v>511.37584442281513</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-10.135101295546331</v>
+        <v>-10.013970812430822</v>
       </c>
       <c r="B27">
-        <v>-2.2079735672629193</v>
+        <v>-2.2815757376495718</v>
       </c>
       <c r="C27">
         <v>511.37584442281513</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-10.726413350419186</v>
+        <v>-10.614517903047391</v>
       </c>
       <c r="B28">
-        <v>-3.0962203067038474</v>
+        <v>-3.1624062776577273</v>
       </c>
       <c r="C28">
         <v>511.37584442281513</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-11.302527396312396</v>
+        <v>-11.200518037647756</v>
       </c>
       <c r="B29">
-        <v>-3.997981431166973</v>
+        <v>-4.0562843091534591</v>
       </c>
       <c r="C29">
         <v>511.37584442281513</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-11.863241094533315</v>
+        <v>-11.771790388170414</v>
       </c>
       <c r="B30">
-        <v>-4.9134368644173678</v>
+        <v>-4.9633720208854264</v>
       </c>
       <c r="C30">
         <v>511.37584442281513</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-12.409138962338956</v>
+        <v>-12.32883811306812</v>
       </c>
       <c r="B31">
-        <v>-5.8420668415783279</v>
+        <v>-5.8832181187394568</v>
       </c>
       <c r="C31">
         <v>511.37584442281513</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-12.941002230973751</v>
+        <v>-12.87233536742219</v>
       </c>
       <c r="B32">
-        <v>-6.7831766756127188</v>
+        <v>-6.8152179378856843</v>
       </c>
       <c r="C32">
         <v>511.37584442281513</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-13.459612131682123</v>
+        <v>-13.402956306313934</v>
       </c>
       <c r="B33">
-        <v>-7.7360716794833921</v>
+        <v>-7.75876681349423</v>
       </c>
       <c r="C33">
         <v>511.37584442281513</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-13.965422045197723</v>
+        <v>-13.9210887723714</v>
       </c>
       <c r="B34">
-        <v>-8.70034869763198</v>
+        <v>-8.7135168808033967</v>
       </c>
       <c r="C34">
         <v>511.37584442281513</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-14.457573950211096</v>
+        <v>-14.425975358409581</v>
       </c>
       <c r="B35">
-        <v>-9.67677070041525</v>
+        <v>-9.6801474753242029</v>
       </c>
       <c r="C35">
         <v>511.37584442281513</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-14.934881974902003</v>
+        <v>-14.916572344790197</v>
       </c>
       <c r="B36">
-        <v>-10.666392189668738</v>
+        <v>-10.659594732635842</v>
       </c>
       <c r="C36">
         <v>511.37584442281513</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-15.396160247450215</v>
+        <v>-15.391836011874981</v>
       </c>
       <c r="B37">
-        <v>-11.670267667227993</v>
+        <v>-11.652794788317527</v>
       </c>
       <c r="C37">
         <v>511.37584442281513</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-15.839424862281133</v>
+        <v>-15.850026485924179</v>
       </c>
       <c r="B38">
-        <v>-12.690161263106271</v>
+        <v>-12.661308174193469</v>
       </c>
       <c r="C38">
         <v>511.37584442281513</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-16.259499778802716</v>
+        <v>-16.286619276792155</v>
       </c>
       <c r="B39">
-        <v>-13.730675620027705</v>
+        <v>-13.689193007067983</v>
       </c>
       <c r="C39">
         <v>511.37584442281513</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-16.650410922668559</v>
+        <v>-16.696393740231777</v>
       </c>
       <c r="B40">
-        <v>-14.797123008894124</v>
+        <v>-14.74113179999039</v>
       </c>
       <c r="C40">
         <v>511.37584442281513</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-17.006184219532258</v>
+        <v>-17.074129231995936</v>
       </c>
       <c r="B41">
-        <v>-15.894815700607367</v>
+        <v>-15.821807066010013</v>
       </c>
       <c r="C41">
         <v>511.37584442281513</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-17.006184219532258</v>
+        <v>-17.074129231995936</v>
       </c>
       <c r="B42">
-        <v>-15.894815700607367</v>
+        <v>-15.821807066010013</v>
       </c>
       <c r="C42">
         <v>511.37584442281513</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-16.37315347185875</v>
+        <v>-16.454719968874954</v>
       </c>
       <c r="B43">
-        <v>-15.043666088683994</v>
+        <v>-14.957894432051377</v>
       </c>
       <c r="C43">
         <v>511.37584442281513</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-15.752601651593365</v>
+        <v>-15.844777292965976</v>
       </c>
       <c r="B44">
-        <v>-14.181419955506852</v>
+        <v>-14.085491003459996</v>
       </c>
       <c r="C44">
         <v>511.37584442281513</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-15.138768179342089</v>
+        <v>-15.239293239630301</v>
       </c>
       <c r="B45">
-        <v>-13.313199727834999</v>
+        <v>-13.209088536168917</v>
       </c>
       <c r="C45">
         <v>511.37584442281513</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-14.525892475710922</v>
+        <v>-14.63325984422924</v>
       </c>
       <c r="B46">
-        <v>-12.444127832427487</v>
+        <v>-12.333178786111194</v>
       </c>
       <c r="C46">
         <v>511.37584442281513</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-13.909003300767854</v>
+        <v>-14.02235663513698</v>
       </c>
       <c r="B47">
-        <v>-11.578624799010864</v>
+        <v>-11.461636881299665</v>
       </c>
       <c r="C47">
         <v>511.37584442281513</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-13.286286772428888</v>
+        <v>-13.405013112779285</v>
       </c>
       <c r="B48">
-        <v>-10.718303569181677</v>
+        <v>-10.595871438066391</v>
       </c>
       <c r="C48">
         <v>511.37584442281513</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-12.656718348072026</v>
+        <v>-12.780346270594805</v>
       </c>
       <c r="B49">
-        <v>-9.8640751875039658</v>
+        <v>-9.7366744448232172</v>
       </c>
       <c r="C49">
         <v>511.37584442281513</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-12.019273485075278</v>
+        <v>-12.1474731020222</v>
       </c>
       <c r="B50">
-        <v>-9.01685069854179</v>
+        <v>-8.8848378899820037</v>
       </c>
       <c r="C50">
         <v>511.37584442281513</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-11.373246837175008</v>
+        <v>-11.505788291851458</v>
       </c>
       <c r="B51">
-        <v>-8.1772573108323581</v>
+        <v>-8.0409046943463327</v>
       </c>
       <c r="C51">
         <v>511.37584442281513</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-10.719209843541044</v>
+        <v>-10.855797290277895</v>
       </c>
       <c r="B52">
-        <v>-7.3447868888055376</v>
+        <v>-7.2044215082866643</v>
       </c>
       <c r="C52">
         <v>511.37584442281513</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-10.058053139701574</v>
+        <v>-10.198283238848173</v>
       </c>
       <c r="B53">
-        <v>-6.5186474608643632</v>
+        <v>-6.3746859145651857</v>
       </c>
       <c r="C53">
         <v>511.37584442281513</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-9.3906673611847857</v>
+        <v>-9.53402927910894</v>
       </c>
       <c r="B54">
-        <v>-5.6980470554118572</v>
+        <v>-5.5509954959440737</v>
       </c>
       <c r="C54">
         <v>511.37584442281513</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-8.7177388684859238</v>
+        <v>-8.8636400238086388</v>
       </c>
       <c r="B55">
-        <v>-4.8823753464501038</v>
+        <v>-4.7328079616733074</v>
       </c>
       <c r="C55">
         <v>511.37584442281513</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-8.0391369219685078</v>
+        <v>-8.1870059705028666</v>
       </c>
       <c r="B56">
-        <v>-4.0717485903774016</v>
+        <v>-3.920221526954041</v>
       </c>
       <c r="C56">
         <v>511.37584442281513</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-7.3545265069631078</v>
+        <v>-7.5038390879490056</v>
       </c>
       <c r="B57">
-        <v>-3.2664646891910905</v>
+        <v>-3.1134945334752131</v>
       </c>
       <c r="C57">
         <v>511.37584442281513</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-6.6635726088002993</v>
+        <v>-6.8138513449044389</v>
       </c>
       <c r="B58">
-        <v>-2.4668215448885205</v>
+        <v>-2.312885322925772</v>
       </c>
       <c r="C58">
         <v>511.37584442281513</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-5.9659807969195056</v>
+        <v>-6.1167896425701054</v>
       </c>
       <c r="B59">
-        <v>-1.6730809712351085</v>
+        <v>-1.5186209053016557</v>
       </c>
       <c r="C59">
         <v>511.37584442281513</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-5.2616189771955719</v>
+        <v>-5.4125406119211723</v>
       </c>
       <c r="B60">
-        <v>-0.885360429068584</v>
+        <v>-0.73080296382682219</v>
       </c>
       <c r="C60">
         <v>511.37584442281513</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.5503956396121952</v>
+        <v>-4.7010258163763616</v>
       </c>
       <c r="B61">
-        <v>-0.1037412909947505</v>
+        <v>0.050498149967769926</v>
       </c>
       <c r="C61">
         <v>511.37584442281513</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-3.8322192741530738</v>
+        <v>-3.9821668193543998</v>
       </c>
       <c r="B62">
-        <v>0.6716950703805874</v>
+        <v>0.82521208455116279</v>
       </c>
       <c r="C62">
         <v>511.37584442281513</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.1072634624396986</v>
+        <v>-3.2561158016697958</v>
       </c>
       <c r="B63">
-        <v>1.4411030074379747</v>
+        <v>1.5934753343129473</v>
       </c>
       <c r="C63">
         <v>511.37584442281513</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.3767621526447202</v>
+        <v>-2.5239474137201889</v>
       </c>
       <c r="B64">
-        <v>2.2055797725033695</v>
+        <v>2.3562517773249274</v>
       </c>
       <c r="C64">
         <v>511.37584442281513</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-1.6422143845785986</v>
+        <v>-1.7869669232990213</v>
       </c>
       <c r="B65">
-        <v>2.9664583428890627</v>
+        <v>3.1147121375794407</v>
       </c>
       <c r="C65">
         <v>511.37584442281513</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-0.90511919805177621</v>
+        <v>-1.0464795981997164</v>
       </c>
       <c r="B66">
-        <v>3.725071695907364</v>
+        <v>3.8700271390688434</v>
       </c>
       <c r="C66">
         <v>511.37584442281513</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-0.16502214087574849</v>
+        <v>-0.30208756067754466</v>
       </c>
       <c r="B67">
-        <v>4.4810157232400094</v>
+        <v>4.6218399163099546</v>
       </c>
       <c r="C67">
         <v>511.37584442281513</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>0.5863452071338221</v>
+        <v>0.45341964916488336</v>
       </c>
       <c r="B68">
-        <v>5.22693797404649</v>
+        <v>5.36368324591749</v>
       </c>
       <c r="C68">
         <v>511.37584442281513</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>1.355396806118135</v>
+        <v>1.225636573346075</v>
       </c>
       <c r="B69">
-        <v>5.9571350218463293</v>
+        <v>6.0905392575354833</v>
       </c>
       <c r="C69">
         <v>511.37584442281513</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2.1333148080499806</v>
+        <v>2.0068815002163238</v>
       </c>
       <c r="B70">
-        <v>6.67944788012138</v>
+        <v>6.8092978508273241</v>
       </c>
       <c r="C70">
         <v>511.37584442281513</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2.910485459521968</v>
+        <v>2.7887793828731584</v>
       </c>
       <c r="B71">
-        <v>7.4024252979367349</v>
+        <v>7.5274707934127427</v>
       </c>
       <c r="C71">
         <v>511.37584442281513</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>3.6893431937743508</v>
+        <v>3.5734580870711947</v>
       </c>
       <c r="B72">
-        <v>8.1239025267280489</v>
+        <v>8.2431495547174265</v>
       </c>
       <c r="C72">
         <v>511.37584442281513</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>4.4739283510465162</v>
+        <v>4.364445777706675</v>
       </c>
       <c r="B73">
-        <v>8.8402868120964442</v>
+        <v>8.953169644424694</v>
       </c>
       <c r="C73">
         <v>511.37584442281513</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>5.262656712926745</v>
+        <v>5.16036890358523</v>
       </c>
       <c r="B74">
-        <v>9.5529868739343691</v>
+        <v>9.6587630314424242</v>
       </c>
       <c r="C74">
         <v>511.37584442281513</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>6.0525091436524825</v>
+        <v>5.9586036602246484</v>
       </c>
       <c r="B75">
-        <v>10.26468739042461</v>
+        <v>10.362283064925492</v>
       </c>
       <c r="C75">
         <v>511.37584442281513</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>6.8403513967089076</v>
+        <v>6.7564269460819535</v>
       </c>
       <c r="B76">
-        <v>10.978175398620017</v>
+        <v>11.066172155792183</v>
       </c>
       <c r="C76">
         <v>511.37584442281513</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>7.6232908803055652</v>
+        <v>7.5513268490656378</v>
       </c>
       <c r="B77">
-        <v>11.696023051176937</v>
+        <v>11.77268329439972</v>
       </c>
       <c r="C77">
         <v>511.37584442281513</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>8.3995167323017039</v>
+        <v>8.34173551195085</v>
       </c>
       <c r="B78">
-        <v>12.419840604295702</v>
+        <v>12.483222727097662</v>
       </c>
       <c r="C78">
         <v>511.37584442281513</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>9.1658892378971277</v>
+        <v>9.1249273076866046</v>
       </c>
       <c r="B79">
-        <v>13.152419957542017</v>
+        <v>13.20023512998913</v>
       </c>
       <c r="C79">
         <v>511.37584442281513</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>9.9168445818049928</v>
+        <v>9.89606472353208</v>
       </c>
       <c r="B80">
-        <v>13.89870857094696</v>
+        <v>13.928059376872655</v>
       </c>
       <c r="C80">
         <v>511.37584442281513</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>10.638590118814177</v>
+        <v>10.643138404770188</v>
       </c>
       <c r="B81">
-        <v>14.670971150901165</v>
+        <v>14.677466927651446</v>
       </c>
       <c r="C81">
         <v>511.37584442281513</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>11.081074970344902</v>
+        <v>11.148203512058567</v>
       </c>
       <c r="B82">
-        <v>15.691558128490108</v>
+        <v>15.643937402454444</v>
       </c>
       <c r="C82">
         <v>511.37584442281513</v>
